--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>weight</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_trap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,6 +526,11 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>weight</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>is_trap</t>
         </is>
       </c>
     </row>
@@ -537,6 +552,9 @@
       <c r="F5" t="n">
         <v>50</v>
       </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -556,6 +574,9 @@
       <c r="F6" t="n">
         <v>35</v>
       </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -574,6 +595,53 @@
       </c>
       <c r="F7" t="n">
         <v>15</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TrapBig</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TrapSmall</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -566,13 +566,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E8" t="n">
         <v>-3</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="n">
         <v>-5</v>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
         <v>-3</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -638,9 +638,31 @@
         <v>-5</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TrapTiny</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="b">
         <v>1</v>
       </c>
     </row>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>is_trap</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -531,6 +541,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>is_trap</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>shape</t>
         </is>
       </c>
     </row>
@@ -555,6 +570,9 @@
       <c r="G5" t="b">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -577,6 +595,9 @@
       <c r="G6" t="b">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -599,6 +620,9 @@
       <c r="G7" t="b">
         <v>0</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -621,6 +645,9 @@
       <c r="G8" t="b">
         <v>1</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -643,6 +670,9 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -664,6 +694,9 @@
       </c>
       <c r="G10" t="b">
         <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RangeFace</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,177 +551,26 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Big</t>
+          <t>RangeFace</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TrapBig</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TrapSmall</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>40</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TrapTiny</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>RangeFace</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
         <v>1</v>
       </c>
     </row>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,31 @@
           <t>shape</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>distance_min_m</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>distance_max_m</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>drift_min_mps</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>drift_max_mps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>stun_ticks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +524,31 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,6 +596,31 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>shape</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>distance_min_m</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>distance_max_m</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>drift_min_mps</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>drift_max_mps</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stun_ticks</t>
         </is>
       </c>
     </row>
@@ -572,6 +647,261 @@
       </c>
       <c r="H5" t="n">
         <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>38</v>
+      </c>
+      <c r="J7" t="n">
+        <v>46</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grail</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>48</v>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KingFlag</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FlowerBasket</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,61 @@
           <t>stun_ticks</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>is_jackpot</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>height_min_m</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>height_max_m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>arc_min_m</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>arc_max_m</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>climb_min_mps</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>climb_max_mps</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>bob_amp_m</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>bob_hz</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>spin_hz</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>lateral_half_m</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +604,61 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -621,6 +731,61 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>stun_ticks</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>is_jackpot</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>height_min_m</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>height_max_m</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>arc_min_m</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>arc_max_m</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>climb_min_mps</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>climb_max_mps</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bob_amp_m</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>bob_hz</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>spin_hz</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>lateral_half_m</t>
         </is>
       </c>
     </row>
@@ -663,24 +828,57 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>WaterBalloon</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -692,7 +890,7 @@
         <v>30</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -701,26 +899,59 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helmet</t>
+          <t>Watermelon</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -735,32 +966,65 @@
         <v>46</v>
       </c>
       <c r="K7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L7" t="n">
         <v>3.5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Plate</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -769,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
@@ -781,26 +1045,59 @@
         <v>7</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grail</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -809,99 +1106,417 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
         <v>55</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KingFlag</t>
+          <t>GoldenBell</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>54</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>32</v>
-      </c>
-      <c r="J10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>75</v>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FlowerBasket</t>
+          <t>Pinata</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="E11" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44</v>
+      </c>
+      <c r="J11" t="n">
+        <v>52</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BirdNest</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>32</v>
       </c>
-      <c r="J11" t="n">
-        <v>50</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J12" t="n">
+        <v>48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CheerFlag</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>75</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KidBalloon</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>32</v>
+      </c>
+      <c r="J14" t="n">
+        <v>48</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="M14" t="n">
         <v>75</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryTarget.xlsx
+++ b/table/Datas/#ArcheryTarget.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,31 @@
           <t>lateral_half_m</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>spawn_side_min_m</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>spawn_side_max_m</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>life_ticks</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>swing_amp_m</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>swing_dip_m</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -659,6 +684,31 @@
           <t>float</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -786,6 +836,31 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>lateral_half_m</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>spawn_side_min_m</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>spawn_side_max_m</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>life_ticks</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>swing_amp_m</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>swing_dip_m</t>
         </is>
       </c>
     </row>
@@ -861,6 +936,21 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -932,6 +1022,21 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,6 +1110,21 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1080,6 +1200,21 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1151,6 +1286,21 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1185,10 +1335,10 @@
         <v>54</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1215,16 +1365,31 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
         <v>8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1258,10 +1423,10 @@
         <v>52</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1288,16 +1453,31 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
@@ -1313,7 +1493,7 @@
         <v>0.75</v>
       </c>
       <c r="E12" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1337,7 +1517,7 @@
         <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1371,6 +1551,21 @@
       </c>
       <c r="X12" t="n">
         <v>10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1386,7 +1581,7 @@
         <v>0.8</v>
       </c>
       <c r="E13" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1410,7 +1605,7 @@
         <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1444,6 +1639,21 @@
       </c>
       <c r="X13" t="n">
         <v>10</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1459,7 +1669,7 @@
         <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1483,7 +1693,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1517,6 +1727,21 @@
       </c>
       <c r="X14" t="n">
         <v>10</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
